--- a/output/pdf_financials_xlsx/ELEM.xlsx
+++ b/output/pdf_financials_xlsx/ELEM.xlsx
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-1.794117</v>
+        <v>-2.214313</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>12.682526</v>
+        <v>12.175536</v>
       </c>
     </row>
     <row r="119">
@@ -3556,7 +3556,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-0.420196</v>
       </c>

--- a/output/pdf_financials_xlsx/ELEM.xlsx
+++ b/output/pdf_financials_xlsx/ELEM.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003216</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.192038</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003216</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.192038</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.73314</v>
+        <v>0.729924</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.91152</v>
+        <v>0.719482</v>
       </c>
     </row>
     <row r="49">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2462,7 +2462,11 @@
           <t>Reclamation deposit 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.011764</v>
       </c>
@@ -3478,7 +3482,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4370,7 +4378,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">

--- a/output/pdf_financials_xlsx/ELEM.xlsx
+++ b/output/pdf_financials_xlsx/ELEM.xlsx
@@ -514,10 +514,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.795968</v>
+        <v>1.969569</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.205164</v>
+        <v>1.446576</v>
       </c>
     </row>
     <row r="8">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.6895250000000001</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.5729379999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.826744</v>
+        <v>1.516269</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.759937</v>
+        <v>1.332875</v>
       </c>
     </row>
     <row r="69">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>1.862945</v>
+        <v>1.17342</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.060643</v>
+        <v>1.487705</v>
       </c>
     </row>
     <row r="76">
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.704801</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.38087</v>
       </c>
     </row>
     <row r="111">
@@ -3054,7 +3054,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.704801</v>
       </c>
@@ -4038,7 +4042,11 @@
           <t>Director fees 13</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.130342</v>
       </c>
@@ -4166,7 +4174,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>0.043259</v>
       </c>
